--- a/feedback_forms/029_employee_retention_interview_form--feedback_forms.xlsx
+++ b/feedback_forms/029_employee_retention_interview_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -719,8 +719,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
